--- a/data/trans_orig/IP31B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28581</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20074</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37384</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23299</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16479</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30675</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>24381</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>63355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56880</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47198</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66768</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51912</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43942</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60185</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>49957</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51193</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>58560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114988</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>95290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128960</t>
+          <t>120079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27221</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36398</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,68%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21408</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14948</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29077</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55305</t>
+          <t>48704</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71983</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4501</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7507</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2136</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13200</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8556</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19741</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24512</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31883</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54537</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45890</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>62077</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40279</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48833</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>33843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>96533</t>
+          <t>95587</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>82412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>106438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13714</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26972</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,01%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>22140</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15503</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29286</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28464</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>873</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,22 +1816,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2272</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10657</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10331</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15922</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5586</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10175</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>24338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27968</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20877</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34168</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>29264</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21601</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34955</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>58,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37099</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49007</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68806</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13224</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6688</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17958</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>35,85%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5616</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2389</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6197</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>28845</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20265</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>38513</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>31925</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20181</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>43370</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30295</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>62220</t>
+          <t>60255</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47298</t>
+          <t>48654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78168</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>87199</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>72946</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>101081</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>44,54%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>82782</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>56071</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>100787</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>47,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76818</t>
+          <t>67918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106398</t>
+          <t>89661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>174821</t>
+          <t>166180</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>137149</t>
+          <t>148604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>197043</t>
+          <t>184294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>54670</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>43474</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>71913</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>27,92%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>80491</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>56365</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>125041</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>37,68%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60255</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76238</t>
+          <t>63436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>140746</t>
+          <t>107617</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>92083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>125644</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18555</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12186</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>26530</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>11775</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>4826</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>32870</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54088</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6524</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10959</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>6668</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11989</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>17835</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11473</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26818</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>17245</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>11336</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24632</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>81158</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>69118</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>93823</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>56,65%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>48,24%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>65044</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>55424</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>74477</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>47,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>64,48%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>64666</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74450</t>
+          <t>55471</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103348</t>
+          <t>74076</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>151672</t>
+          <t>145824</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>136670</t>
+          <t>130501</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>170142</t>
+          <t>160744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>32408</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>23817</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>42188</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>25044</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17953</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>32918</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46905</t>
+          <t>32362</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>57008</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49884</t>
+          <t>45742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>69010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>9916</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1761</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>9044</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>6354</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>13085</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>3790</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>7426</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>13288</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>8172</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>20952</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>20,18%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>16849</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>24438</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19722</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>33758</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>25968</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>41367</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>35333</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>28043</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>42564</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>52,2%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34304</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>70138</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>58994</t>
+          <t>60250</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>80132</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8621</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>20576</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10666</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>16442</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>8472</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>6597</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2938</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>12638</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>3802</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>7982</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>112081</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>95901</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>131870</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>119415</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>99769</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>140224</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>114742</t>
+          <t>123894</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>97017</t>
+          <t>107012</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>134393</t>
+          <t>142841</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>234157</t>
+          <t>235974</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>205212</t>
+          <t>212498</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>258892</t>
+          <t>262923</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>341500</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>315010</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>365063</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>50,83%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>440</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>304615</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>259573</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>331116</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>47,51%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>40,48%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>361846</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>334393</t>
+          <t>281990</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>391763</t>
+          <t>324413</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>666460</t>
+          <t>642688</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>613224</t>
+          <t>608643</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>674877</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>161500</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>141817</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>185326</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>170980</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>142838</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>246991</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>38,52%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>183534</t>
+          <t>144097</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>160130</t>
+          <t>126320</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>207944</t>
+          <t>161448</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>354515</t>
+          <t>305597</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>318795</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>431466</t>
+          <t>332113</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>36176</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>27725</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>48085</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>24669</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>15543</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>47686</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>54282</t>
+          <t>25263</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>54361</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>67502</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>20604</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>27989</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>21517</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>14640</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>29824</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>19270</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>30799</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>57123</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
